--- a/data/trans_camb/IP1018-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,0</t>
+          <t>-2,6; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,0</t>
+          <t>-2,6; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,0</t>
+          <t>-1,56; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,53</t>
+          <t>-0,68; 2,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,0</t>
+          <t>-1,58; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,18</t>
+          <t>-0,86; 1,16</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,0</t>
+          <t>-2,26; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,0</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,0</t>
+          <t>-1,16; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,25</t>
+          <t>-0,99; 0,22</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,0</t>
+          <t>-2,41; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,71</t>
+          <t>-1,47; 0,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,0</t>
+          <t>-1,76; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,37</t>
+          <t>-0,82; 0,37</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,0</t>
+          <t>-0,65; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,43</t>
+          <t>-0,35; 0,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; -0,07</t>
+          <t>-0,75; -0,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,44</t>
+          <t>-0,45; 0,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; -0,09</t>
+          <t>-0,53; -0,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,28</t>
+          <t>-0,28; 0,32</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-82,47; 328,82</t>
+          <t>-82,21; 395,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1018-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,0</t>
+          <t>-2,59; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,0</t>
+          <t>-2,58; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,0</t>
+          <t>-1,73; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,95</t>
+          <t>-0,68; 3,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,0</t>
+          <t>-1,45; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,16</t>
+          <t>-0,85; 1,16</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,0</t>
+          <t>-2,0; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,59</t>
+          <t>-1,06; 0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,0</t>
+          <t>-1,85; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,0</t>
+          <t>-1,15; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,22</t>
+          <t>-0,99; 0,26</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,71</t>
+          <t>-1,94; 0,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,0</t>
+          <t>-1,26; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,37</t>
+          <t>-1,01; 0,37</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,0</t>
+          <t>-0,71; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,43</t>
+          <t>-0,4; 0,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; -0,07</t>
+          <t>-0,7; -0,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,46</t>
+          <t>-0,46; 0,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; -0,09</t>
+          <t>-0,53; -0,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,32</t>
+          <t>-0,29; 0,36</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-82,21; 395,5</t>
+          <t>-78,66; 389,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1018-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-0,52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,52</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,0</t>
+          <t>-1,55; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 0,0</t>
+          <t>-0,68; 3,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,0</t>
+          <t>-2,61; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,65</t>
+          <t>-2,63; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,0</t>
+          <t>-1,35; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,16</t>
+          <t>-0,85; 1,18</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>114,37%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114,37%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,32</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,04</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,0</t>
+          <t>-1,29; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,59</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,0</t>
+          <t>-1,68; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,0</t>
+          <t>-1,05; 0,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,0</t>
+          <t>-0,99; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,26</t>
+          <t>-0,97; 0,25</t>
         </is>
       </c>
     </row>
@@ -830,17 +830,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-13,01%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,48</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,42; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,93; 0,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,0</t>
+          <t>-1,4; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,37</t>
+          <t>-0,76; 0,37</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-26,63%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-26,63%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,59</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,06</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>-0,73; -0,07</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>-0,43; 0,44</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>-0,71; 0,0</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-0,4; 0,44</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-0,7; -0,07</t>
-        </is>
-      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,45</t>
+          <t>-0,37; 0,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; -0,05</t>
+          <t>-0,54; -0,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,36</t>
+          <t>-0,28; 0,28</t>
         </is>
       </c>
     </row>
@@ -1298,17 +1298,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>-15,44%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>28,43%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-15,44%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-78,66; 389,53</t>
+          <t>-82,47; 328,82</t>
         </is>
       </c>
     </row>
